--- a/docs/PX案件チェックシート_多治見市大薮町.xlsx
+++ b/docs/PX案件チェックシート_多治見市大薮町.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>重ねるハザードマップで「洪水浸水想定区域」をON。 / 重ねるハザードマップ公開タイル（disaportaldata）で地点判定 2026-10-19。内水は自治体マップで要確認</t>
+          <t>重ねるハザードマップで「洪水浸水想定区域」をON。 / reinfolib 洪水/高潮/津波 浸水想定区域より自動判定（不動産情報ライブラリ 2026-10-19 取得）／ 別データでも同判定：重ねるハザードマップ公開タイル（disaportaldata）で地点判定 2026-10-19。内水は自治体マップで要確認</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>重ねるハザードマップで「土砂災害（特別）警戒区域」をON。 / 重ねるハザードマップ公開タイルで地点判定。区域の縁から約6〜12m内側。敷地が区域にどこまで掛かるか要確認（岐阜県 土砂災害警戒区域等マップ）</t>
+          <t>重ねるハザードマップで「土砂災害（特別）警戒区域」をON。 / reinfolib XKT029より自動判定（不動産情報ライブラリ 2026-10-19 取得）／ 別データでも同判定：重ねるハザードマップ公開タイルで地点判定。区域の縁から約6〜12m内側。敷地が区域にどこまで掛かるか要確認（岐阜県 土砂災害警戒区域等マップ）</t>
         </is>
       </c>
       <c r="H7" s="9" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>J-SHIS表層地盤＋各都道府県の液状化マップで確認。 / J-SHIS API（250mメッシュ）より。岐阜県液状化マップでも確認推奨</t>
+          <t>J-SHIS表層地盤＋各都道府県の液状化マップで確認。 / reinfolib XKT025（地形区分に基づく液状化発生傾向）より自動判定（不動産情報ライブラリ 2026-10-19 取得）／ 別データでも同判定：J-SHIS API（250mメッシュ）より。岐阜県液状化マップでも確認推奨</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>自治体の都市計画情報(web GIS)で区域区分を確認。 / 国土数値情報 都市地域(A09, 2018年度)で点内判定</t>
+          <t>自治体の都市計画情報(web GIS)で区域区分を確認。 / reinfolib XKT001より自動判定（都市計画区域 / 市街化調整区域）（不動産情報ライブラリ 2026-10-19 取得）／ 別データでも同判定：国土数値情報 都市地域(A09, 2018年度)で点内判定</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>同上。市街化調整区域内かを確認。 / 国土数値情報 都市地域(A09, 2018年度)で点内判定。区域境界から約1km内側で判定は安定。多治見市は調整区域に系統用蓄電池の許可基準を定めておらず『設置（建築）できない』と公表（市HP 令和8年5月15日お知らせ）</t>
+          <t>同上。市街化調整区域内かを確認。 / reinfolib XKT001より自動判定（都市計画区域 / 市街化調整区域）（不動産情報ライブラリ 2026-10-19 取得）／ 別データでも同判定：国土数値情報 都市地域(A09, 2018年度)で点内判定。区域境界から約1km内側で判定は安定。多治見市は調整区域に系統用蓄電池の許可基準を定めておらず『設置（建築）できない』と公表（市HP 令和8年5月15日お知らせ）</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>自治体の都市計画情報で用途地域を確認（指定なしの場合あり）。 / 調整区域のため用途地域の指定なし</t>
+          <t>自治体の都市計画情報で用途地域を確認（指定なしの場合あり）。 / reinfolib XKT002より自動判定（不動産情報ライブラリ 2026-10-19 取得）／ 別データでも同判定：調整区域のため用途地域の指定なし</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -1253,19 +1253,19 @@
           <t>13. 公園</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>該当なし</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>検索リンク（要確認）</t>
+          <t>検索リンク（参考）</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>自然公園・都市公園の区域内かを確認。</t>
+          <t>自然公園・都市公園の区域内かを確認。 / reinfolib XKT019（自然公園地域）より自動判定（不動産情報ライブラリ 2026-10-19 取得）</t>
         </is>
       </c>
       <c r="H15" s="9" t="inlineStr">
@@ -2123,7 +2123,7 @@
       <c r="O18" s="21" t="inlineStr"/>
       <c r="P18" s="21" t="inlineStr">
         <is>
-          <t>土砂災害警戒区域（土石流）に該当（重ねるハザードマップで地点判定）</t>
+          <t>土砂災害危険箇所/警戒区域に該当 (reinfolib XKT029)／重ねるハザードマップでも同判定</t>
         </is>
       </c>
     </row>

--- a/docs/PX案件チェックシート_多治見市大薮町.xlsx
+++ b/docs/PX案件チェックシート_多治見市大薮町.xlsx
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>可能性高い（地点の東側一帯が水田）</t>
+          <t>農業振興地域内。農用地区域（青地）の外だが、最寄りの農用地区域まで約90m。東側の水田は農用地区域の可能性</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>地点はGoogleマップ航空写真（座標）で確認。農地区分はeMAFF農地ナビ（住所/地番検索）、種別(1/2/3種)は農業委員会へ照会。 / GSI航空写真で目視。地目・農振農用地区域かは eMAFF農地ナビ／多治見市農業委員会で要確認</t>
+          <t>地点はGoogleマップ航空写真（座標）で確認。農地区分はeMAFF農地ナビ（住所/地番検索）、種別(1/2/3種)は農業委員会へ照会。 / 国土数値情報 農業地域(A12・2002年度の区域)で点内判定＋GSI航空写真で目視。データが古いため、地目・青地/白地は多治見市農業委員会／eMAFF農地ナビ（住所検索）で要確認</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -2802,38 +2802,46 @@
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="9" t="inlineStr"/>
-      <c r="B38" s="19" t="n"/>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr"/>
+      <c r="B38" s="21" t="n"/>
+      <c r="C38" s="20" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D38" s="8" t="inlineStr">
+      <c r="D38" s="22" t="inlineStr">
         <is>
           <t>農振法</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="22" t="inlineStr">
         <is>
           <t>農振除外手続</t>
         </is>
       </c>
-      <c r="F38" s="8" t="inlineStr">
+      <c r="F38" s="22" t="inlineStr">
         <is>
           <t>農用地区内か</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="19" t="inlineStr"/>
-      <c r="I38" s="19" t="inlineStr"/>
-      <c r="J38" s="19" t="inlineStr"/>
-      <c r="K38" s="19" t="inlineStr"/>
-      <c r="L38" s="19" t="inlineStr"/>
-      <c r="M38" s="19" t="inlineStr"/>
-      <c r="N38" s="19" t="inlineStr"/>
-      <c r="O38" s="19" t="inlineStr"/>
-      <c r="P38" s="19" t="inlineStr"/>
+      <c r="G38" s="20" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr"/>
+      <c r="I38" s="21" t="inlineStr"/>
+      <c r="J38" s="21" t="inlineStr"/>
+      <c r="K38" s="21" t="inlineStr"/>
+      <c r="L38" s="21" t="inlineStr"/>
+      <c r="M38" s="21" t="inlineStr"/>
+      <c r="N38" s="21" t="inlineStr"/>
+      <c r="O38" s="21" t="inlineStr"/>
+      <c r="P38" s="21" t="inlineStr">
+        <is>
+          <t>農業振興地域内（農用地区域外の見込み・旧データ）。青地なら農振除外が必要</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="23" t="inlineStr">
@@ -3393,7 +3401,7 @@
       </c>
       <c r="D4" s="27" t="inlineStr">
         <is>
-          <t>大針変電所 空容量33MW（1.24km）／可児 38MW（3.5km）／久々利 25MW（4.3km）</t>
+          <t>大針変電所(77/6.6kV) 空容量31MW（1.24km）／可児 38MW（3.5km）／久々利 26MW（4.3km）</t>
         </is>
       </c>
       <c r="E4" s="28" t="inlineStr">
@@ -3408,7 +3416,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>空きあり=良／要確認=注意／空きなし・不明=リスク。マップは申込ベースで埋まるため最新性に注意。 / リポジトリの変電所DB（中部 公表資料）より。最新は中部電力PG空き容量マップで確認</t>
+          <t>空きあり=良／要確認=注意／空きなし・不明=リスク。マップは申込ベースで埋まるため最新性に注意。 / 蓄電所ネット（中部電力PG 2026/8/17公表値）。大針はリポジトリDBの33MWから31MWに減少</t>
         </is>
       </c>
     </row>
@@ -3428,10 +3436,14 @@
           <t>先行申込案件の状況</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>未確認</t>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>大針の空容量が2MW減少＝他案件の申込が入った可能性。岐阜県内の蓄電所案件8件のうち多治見・可児周辺はなし</t>
+        </is>
+      </c>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>注意</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -3441,7 +3453,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>先着優先のため、検討中に容量を先取りされるリスクを確認。</t>
+          <t>先着優先のため、検討中に容量を先取りされるリスクを確認。 / 蓄電所ネット プロジェクト一覧（2026-10-19確認）</t>
         </is>
       </c>
     </row>
@@ -3500,12 +3512,12 @@
       </c>
       <c r="D7" s="27" t="inlineStr">
         <is>
-          <t>N-1電制不可・出力制御あり（大針/可児/久々利とも）</t>
-        </is>
-      </c>
-      <c r="E7" s="29" t="inlineStr">
-        <is>
-          <t>注意</t>
+          <t>ノンファーム接続 対象外／N-1電制 不可（大針）</t>
+        </is>
+      </c>
+      <c r="E7" s="28" t="inlineStr">
+        <is>
+          <t>良</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -3515,7 +3527,7 @@
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>該当時は出力制御リスクを事業収支に織り込む（注意）。</t>
+          <t>該当時は出力制御リスクを事業収支に織り込む（注意）。 / 蓄電所ネット 大針変電所ページ</t>
         </is>
       </c>
     </row>

--- a/docs/PX案件チェックシート_多治見市大薮町.xlsx
+++ b/docs/PX案件チェックシート_多治見市大薮町.xlsx
@@ -1661,7 +1661,7 @@
       <c r="O5" s="21" t="inlineStr"/>
       <c r="P5" s="21" t="inlineStr">
         <is>
-          <t>市街化調整区域。多治見市は調整区域での系統用蓄電池の許可基準なし＝原則設置不可（市HP）。開発指導課へ要事前相談</t>
+          <t>市街化調整区域。多治見市は許可基準なし＝許可要のものは設置不可。ただし事業者が電気事業法の発電事業者（1,000kW以上の設備の合計が1万kW超で届出済み）なら『適用除外』になり得る。経産省受領印付きの発電事業届出書等を開発指導課で確認のうえ判断（市PDF ※3）</t>
         </is>
       </c>
     </row>

--- a/docs/PX案件チェックシート_多治見市大薮町.xlsx
+++ b/docs/PX案件チェックシート_多治見市大薮町.xlsx
@@ -919,7 +919,7 @@
       </c>
       <c r="E3" s="15" t="inlineStr">
         <is>
-          <t>岐阜県多治見市大薮町（地番未確定）</t>
+          <t>岐阜県多治見市大薮町（地番（推定）: 1397番1・1430番2・1425番4・1429番2ほか）</t>
         </is>
       </c>
       <c r="F3" s="16" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>住所→座標は代表点（数百m誤差）。緯度経度があればそれを優先。住居表示と地番は要照合。 / 国土地理院 逆ジオコーダで町名まで取得。地番は登記・公図で要確認</t>
+          <t>住所→座標は代表点（数百m誤差）。緯度経度があればそれを優先。住居表示と地番は要照合。 / 国土地理院 逆ジオコーダで町名まで取得。地番は登記・公図で要確認 / 地番は登記所備付地図から筆ポリゴンへの位置合わせで推定（筆の境目付近（候補あり））。登記簿・公図で確認</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps?q=35.38001,137.06507</t>
+          <t>https://map.maff.go.jp/</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>地点はGoogleマップ航空写真（座標）で確認。農地区分はeMAFF農地ナビ（住所/地番検索）、種別(1/2/3種)は農業委員会へ照会。 / 国土数値情報 農業地域(A12・2002年度の区域)で点内判定＋GSI航空写真で目視。データが古いため、地目・青地/白地は多治見市農業委員会／eMAFF農地ナビ（住所検索）で要確認</t>
+          <t>地点はGoogleマップ航空写真（座標）で確認。農地区分はeMAFF農地ナビ（住所/地番検索）、種別(1/2/3種)は農業委員会へ照会。 / 国土数値情報 農業地域(A12・2002年度の区域)で点内判定＋GSI航空写真で目視。データが古いため、地目・青地/白地は多治見市農業委員会／eMAFF農地ナビ（住所検索）で要確認 / eMAFF農地ナビ（https://map.maff.go.jp/）の「住所・地番で探す」に『大薮町1397-1』と入力（都道府県・市区町村を選んでから）。表示された筆で、地目（田・畑）と農振区分（農用地区域=青地／それ以外=白地）を確認する。 地点は筆の境目付近のため、候補の1397番1・1430番2・1425番4・1429番2を順に確認する。 地番は公図の形を農地の区画（筆ポリゴン）に重ねて推定したもの。登記簿・公図で必ず確認する。 位置合わせできなかった地図（大薮町２０Ａ０２。山林・宅地など農地以外の筆）にまたがる可能性もある。</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
